--- a/it_request_forms/015_e_commerce_app_integration_request_form--it_request_forms.xlsx
+++ b/it_request_forms/015_e_commerce_app_integration_request_form--it_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>app_details</t>
+          <t>app_details_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>App Details</t>
+          <t>App Details 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>integration_notes</t>
+          <t>integration_notes_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Integration Notes</t>
+          <t>Integration Notes 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>next_steps_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Next Steps</t>
+          <t>Next Steps 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>integration_issues</t>
+          <t>integration_issues_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Integration Issues</t>
+          <t>Integration Issues 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>integration_type</t>
+          <t>integration_type_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Integration Type</t>
+          <t>Integration Type 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>integration_scope</t>
+          <t>integration_scope_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Integration Scope</t>
+          <t>Integration Scope 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1358,7 +1358,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>next_steps_choices</t>
+          <t>next_steps_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>next_steps_choices</t>
+          <t>next_steps_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1392,7 +1392,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>next_steps_choices</t>
+          <t>next_steps_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1409,7 +1409,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>integration_issues_choices</t>
+          <t>integration_issues_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1426,7 +1426,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>integration_issues_choices</t>
+          <t>integration_issues_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1443,7 +1443,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>integration_issues_choices</t>
+          <t>integration_issues_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1460,7 +1460,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>integration_type_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1477,7 +1477,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>integration_type_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1494,7 +1494,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>integration_type_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
